--- a/data/products_export.xlsx
+++ b/data/products_export.xlsx
@@ -381,7 +381,7 @@
         <v>500</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -415,7 +415,7 @@
         <v>700</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
